--- a/artfynd/A 24162-2026 artfynd.xlsx
+++ b/artfynd/A 24162-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137490715</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137490703</v>
       </c>
       <c r="B3" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>137490721</v>
       </c>
       <c r="B4" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>137490716</v>
       </c>
       <c r="B5" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>137490705</v>
       </c>
       <c r="B6" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
